--- a/template.xlsx
+++ b/template.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\techtextile\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\techtextile\Downloads\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="570" yWindow="105" windowWidth="22005" windowHeight="12435"/>
   </bookViews>
   <sheets>
-    <sheet name="분리막" sheetId="1" r:id="rId1"/>
+    <sheet name="견적서" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">분리막!$A$2:$T$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">견적서!$A$2:$T$28</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
@@ -3501,164 +3501,164 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="30" fillId="24" borderId="9" xfId="825" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="30" fillId="24" borderId="11" xfId="825" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="30" fillId="24" borderId="6" xfId="825" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="31" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="31" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="30" fillId="24" borderId="11" xfId="825" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="30" fillId="24" borderId="6" xfId="825" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="30" fillId="24" borderId="9" xfId="825" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="870">
@@ -4963,23 +4963,23 @@
       <c r="T1" s="1"/>
     </row>
     <row r="2" spans="1:20" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="57"/>
+      <c r="N2" s="57"/>
+      <c r="O2" s="57"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -5009,123 +5009,123 @@
       <c r="T3" s="1"/>
     </row>
     <row r="4" spans="1:20" ht="22.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="35" t="s">
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="68" t="s">
         <v>4</v>
       </c>
       <c r="J4" s="6"/>
-      <c r="K4" s="25" t="s">
+      <c r="K4" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="38" t="s">
+      <c r="L4" s="58"/>
+      <c r="M4" s="58"/>
+      <c r="N4" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="O4" s="38"/>
-      <c r="P4" s="38"/>
-      <c r="Q4" s="38"/>
-      <c r="R4" s="38"/>
-      <c r="S4" s="38"/>
-      <c r="T4" s="38"/>
+      <c r="O4" s="71"/>
+      <c r="P4" s="71"/>
+      <c r="Q4" s="71"/>
+      <c r="R4" s="71"/>
+      <c r="S4" s="71"/>
+      <c r="T4" s="71"/>
     </row>
     <row r="5" spans="1:20" ht="22.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="27"/>
-      <c r="B5" s="28"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="36"/>
+      <c r="A5" s="60"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="69"/>
       <c r="J5" s="6"/>
-      <c r="K5" s="27" t="s">
+      <c r="K5" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="L5" s="27"/>
-      <c r="M5" s="27"/>
-      <c r="N5" s="39" t="s">
+      <c r="L5" s="60"/>
+      <c r="M5" s="60"/>
+      <c r="N5" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="O5" s="39"/>
-      <c r="P5" s="39"/>
+      <c r="O5" s="52"/>
+      <c r="P5" s="52"/>
       <c r="Q5" s="7"/>
-      <c r="R5" s="39" t="s">
+      <c r="R5" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="S5" s="39"/>
+      <c r="S5" s="52"/>
       <c r="T5" s="7" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="22.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="28"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
+      <c r="B6" s="61"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
       <c r="I6" s="8" t="s">
         <v>5</v>
       </c>
       <c r="J6" s="6"/>
-      <c r="K6" s="27" t="s">
+      <c r="K6" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="L6" s="27"/>
-      <c r="M6" s="27"/>
-      <c r="N6" s="39" t="s">
+      <c r="L6" s="60"/>
+      <c r="M6" s="60"/>
+      <c r="N6" s="52" t="s">
         <v>44</v>
       </c>
-      <c r="O6" s="39"/>
-      <c r="P6" s="39"/>
-      <c r="Q6" s="39"/>
-      <c r="R6" s="39"/>
-      <c r="S6" s="39"/>
-      <c r="T6" s="39"/>
+      <c r="O6" s="52"/>
+      <c r="P6" s="52"/>
+      <c r="Q6" s="52"/>
+      <c r="R6" s="52"/>
+      <c r="S6" s="52"/>
+      <c r="T6" s="52"/>
     </row>
     <row r="7" spans="1:20" ht="22.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="30"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="37" t="s">
+      <c r="B7" s="63"/>
+      <c r="C7" s="63"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="67"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="I7" s="30"/>
+      <c r="I7" s="63"/>
       <c r="J7" s="6"/>
-      <c r="K7" s="29" t="s">
+      <c r="K7" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="L7" s="29"/>
-      <c r="M7" s="29"/>
-      <c r="N7" s="40"/>
-      <c r="O7" s="40"/>
-      <c r="P7" s="40"/>
+      <c r="L7" s="62"/>
+      <c r="M7" s="62"/>
+      <c r="N7" s="51"/>
+      <c r="O7" s="51"/>
+      <c r="P7" s="51"/>
       <c r="Q7" s="9"/>
-      <c r="R7" s="40" t="s">
+      <c r="R7" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="S7" s="40"/>
+      <c r="S7" s="51"/>
       <c r="T7" s="19"/>
     </row>
     <row r="8" spans="1:20" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -5151,43 +5151,43 @@
       <c r="T8" s="6"/>
     </row>
     <row r="9" spans="1:20" ht="30" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="41" t="s">
+      <c r="A9" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="41"/>
-      <c r="C9" s="41"/>
+      <c r="B9" s="53"/>
+      <c r="C9" s="53"/>
       <c r="D9" s="10"/>
       <c r="E9" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="42">
+      <c r="F9" s="54">
         <f>O21</f>
         <v>0</v>
       </c>
-      <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
-      <c r="I9" s="42"/>
-      <c r="J9" s="42"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="54"/>
+      <c r="I9" s="54"/>
+      <c r="J9" s="54"/>
       <c r="K9" s="11" t="s">
         <v>17</v>
       </c>
       <c r="L9" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="M9" s="43">
+      <c r="M9" s="55">
         <f>O21</f>
         <v>0</v>
       </c>
-      <c r="N9" s="43"/>
-      <c r="O9" s="43"/>
-      <c r="P9" s="43"/>
+      <c r="N9" s="55"/>
+      <c r="O9" s="55"/>
+      <c r="P9" s="55"/>
       <c r="Q9" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="R9" s="41" t="s">
+      <c r="R9" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="S9" s="41"/>
+      <c r="S9" s="53"/>
       <c r="T9" s="15"/>
     </row>
     <row r="10" spans="1:20" ht="7.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -5216,33 +5216,33 @@
       <c r="A11" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21" t="s">
+      <c r="C11" s="72"/>
+      <c r="D11" s="72"/>
+      <c r="E11" s="72"/>
+      <c r="F11" s="72" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="21" t="s">
+      <c r="G11" s="72"/>
+      <c r="H11" s="72"/>
+      <c r="I11" s="72"/>
+      <c r="J11" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="K11" s="21"/>
-      <c r="L11" s="21"/>
-      <c r="M11" s="22" t="s">
+      <c r="K11" s="72"/>
+      <c r="L11" s="72"/>
+      <c r="M11" s="73" t="s">
         <v>46</v>
       </c>
-      <c r="N11" s="21"/>
-      <c r="O11" s="22" t="s">
+      <c r="N11" s="72"/>
+      <c r="O11" s="73" t="s">
         <v>42</v>
       </c>
-      <c r="P11" s="21"/>
-      <c r="Q11" s="21"/>
-      <c r="R11" s="21"/>
+      <c r="P11" s="72"/>
+      <c r="Q11" s="72"/>
+      <c r="R11" s="72"/>
       <c r="S11" s="14" t="s">
         <v>41</v>
       </c>
@@ -5254,263 +5254,263 @@
       <c r="A12" s="20">
         <v>1</v>
       </c>
-      <c r="B12" s="70"/>
-      <c r="C12" s="68"/>
-      <c r="D12" s="68"/>
-      <c r="E12" s="69"/>
-      <c r="F12" s="71"/>
-      <c r="G12" s="72"/>
-      <c r="H12" s="72"/>
-      <c r="I12" s="73"/>
-      <c r="J12" s="65"/>
-      <c r="K12" s="65"/>
-      <c r="L12" s="65"/>
-      <c r="M12" s="66"/>
-      <c r="N12" s="67"/>
-      <c r="O12" s="65">
+      <c r="B12" s="24"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="30"/>
+      <c r="L12" s="30"/>
+      <c r="M12" s="31"/>
+      <c r="N12" s="32"/>
+      <c r="O12" s="30">
         <f t="shared" ref="O12" si="0">J12*M12</f>
         <v>0</v>
       </c>
-      <c r="P12" s="65"/>
-      <c r="Q12" s="65"/>
-      <c r="R12" s="65"/>
+      <c r="P12" s="30"/>
+      <c r="Q12" s="30"/>
+      <c r="R12" s="30"/>
       <c r="S12" s="17"/>
       <c r="T12" s="18"/>
     </row>
     <row r="13" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="64" t="s">
+      <c r="A13" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="52"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="52"/>
-      <c r="H13" s="52"/>
-      <c r="I13" s="52"/>
-      <c r="J13" s="52"/>
-      <c r="K13" s="52"/>
-      <c r="L13" s="52"/>
-      <c r="M13" s="52"/>
-      <c r="N13" s="52"/>
-      <c r="O13" s="55">
+      <c r="B13" s="28"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="28"/>
+      <c r="K13" s="28"/>
+      <c r="L13" s="28"/>
+      <c r="M13" s="28"/>
+      <c r="N13" s="28"/>
+      <c r="O13" s="29">
         <f>SUM(O12:R12)</f>
         <v>0</v>
       </c>
-      <c r="P13" s="55"/>
-      <c r="Q13" s="55"/>
-      <c r="R13" s="55"/>
-      <c r="S13" s="52"/>
-      <c r="T13" s="53"/>
+      <c r="P13" s="29"/>
+      <c r="Q13" s="29"/>
+      <c r="R13" s="29"/>
+      <c r="S13" s="28"/>
+      <c r="T13" s="33"/>
     </row>
     <row r="14" spans="1:20" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="56" t="s">
+      <c r="A14" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="57"/>
-      <c r="C14" s="57"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="57"/>
-      <c r="H14" s="57"/>
-      <c r="I14" s="57"/>
-      <c r="J14" s="52" t="s">
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="35"/>
+      <c r="J14" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="K14" s="52"/>
-      <c r="L14" s="52"/>
-      <c r="M14" s="52"/>
-      <c r="N14" s="52"/>
-      <c r="O14" s="54"/>
-      <c r="P14" s="55"/>
-      <c r="Q14" s="55"/>
-      <c r="R14" s="55"/>
-      <c r="S14" s="52"/>
-      <c r="T14" s="53"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="28"/>
+      <c r="M14" s="28"/>
+      <c r="N14" s="28"/>
+      <c r="O14" s="38"/>
+      <c r="P14" s="29"/>
+      <c r="Q14" s="29"/>
+      <c r="R14" s="29"/>
+      <c r="S14" s="28"/>
+      <c r="T14" s="33"/>
     </row>
     <row r="15" spans="1:20" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="56"/>
-      <c r="B15" s="57"/>
-      <c r="C15" s="57"/>
-      <c r="D15" s="57"/>
-      <c r="E15" s="57"/>
-      <c r="F15" s="57"/>
-      <c r="G15" s="57"/>
-      <c r="H15" s="57"/>
-      <c r="I15" s="57"/>
-      <c r="J15" s="52" t="s">
+      <c r="A15" s="34"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="35"/>
+      <c r="J15" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="K15" s="52"/>
-      <c r="L15" s="52"/>
-      <c r="M15" s="52"/>
-      <c r="N15" s="52"/>
-      <c r="O15" s="54">
+      <c r="K15" s="28"/>
+      <c r="L15" s="28"/>
+      <c r="M15" s="28"/>
+      <c r="N15" s="28"/>
+      <c r="O15" s="38">
         <v>0</v>
       </c>
-      <c r="P15" s="55"/>
-      <c r="Q15" s="55"/>
-      <c r="R15" s="55"/>
-      <c r="S15" s="52"/>
-      <c r="T15" s="53"/>
+      <c r="P15" s="29"/>
+      <c r="Q15" s="29"/>
+      <c r="R15" s="29"/>
+      <c r="S15" s="28"/>
+      <c r="T15" s="33"/>
     </row>
     <row r="16" spans="1:20" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="56"/>
-      <c r="B16" s="57"/>
-      <c r="C16" s="57"/>
-      <c r="D16" s="57"/>
-      <c r="E16" s="57"/>
-      <c r="F16" s="57"/>
-      <c r="G16" s="57"/>
-      <c r="H16" s="57"/>
-      <c r="I16" s="57"/>
-      <c r="J16" s="52" t="s">
+      <c r="A16" s="34"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="35"/>
+      <c r="J16" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="K16" s="52"/>
-      <c r="L16" s="52"/>
-      <c r="M16" s="52"/>
-      <c r="N16" s="52"/>
-      <c r="O16" s="54">
+      <c r="K16" s="28"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="28"/>
+      <c r="N16" s="28"/>
+      <c r="O16" s="38">
         <v>0</v>
       </c>
-      <c r="P16" s="55"/>
-      <c r="Q16" s="55"/>
-      <c r="R16" s="55"/>
-      <c r="S16" s="52"/>
-      <c r="T16" s="53"/>
+      <c r="P16" s="29"/>
+      <c r="Q16" s="29"/>
+      <c r="R16" s="29"/>
+      <c r="S16" s="28"/>
+      <c r="T16" s="33"/>
     </row>
     <row r="17" spans="1:20" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="56"/>
-      <c r="B17" s="57"/>
-      <c r="C17" s="57"/>
-      <c r="D17" s="57"/>
-      <c r="E17" s="57"/>
-      <c r="F17" s="57"/>
-      <c r="G17" s="57"/>
-      <c r="H17" s="57"/>
-      <c r="I17" s="57"/>
-      <c r="J17" s="52" t="s">
+      <c r="A17" s="34"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="K17" s="52"/>
-      <c r="L17" s="52"/>
-      <c r="M17" s="52"/>
-      <c r="N17" s="52"/>
-      <c r="O17" s="54">
+      <c r="K17" s="28"/>
+      <c r="L17" s="28"/>
+      <c r="M17" s="28"/>
+      <c r="N17" s="28"/>
+      <c r="O17" s="38">
         <v>0</v>
       </c>
-      <c r="P17" s="55"/>
-      <c r="Q17" s="55"/>
-      <c r="R17" s="55"/>
-      <c r="S17" s="52"/>
-      <c r="T17" s="53"/>
+      <c r="P17" s="29"/>
+      <c r="Q17" s="29"/>
+      <c r="R17" s="29"/>
+      <c r="S17" s="28"/>
+      <c r="T17" s="33"/>
     </row>
     <row r="18" spans="1:20" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="56"/>
-      <c r="B18" s="57"/>
-      <c r="C18" s="57"/>
-      <c r="D18" s="57"/>
-      <c r="E18" s="57"/>
-      <c r="F18" s="57"/>
-      <c r="G18" s="57"/>
-      <c r="H18" s="57"/>
-      <c r="I18" s="57"/>
-      <c r="J18" s="52" t="s">
+      <c r="A18" s="34"/>
+      <c r="B18" s="35"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="K18" s="52"/>
-      <c r="L18" s="52"/>
-      <c r="M18" s="52"/>
-      <c r="N18" s="52"/>
-      <c r="O18" s="54">
+      <c r="K18" s="28"/>
+      <c r="L18" s="28"/>
+      <c r="M18" s="28"/>
+      <c r="N18" s="28"/>
+      <c r="O18" s="38">
         <v>0</v>
       </c>
-      <c r="P18" s="55"/>
-      <c r="Q18" s="55"/>
-      <c r="R18" s="55"/>
-      <c r="S18" s="52"/>
-      <c r="T18" s="53"/>
+      <c r="P18" s="29"/>
+      <c r="Q18" s="29"/>
+      <c r="R18" s="29"/>
+      <c r="S18" s="28"/>
+      <c r="T18" s="33"/>
     </row>
     <row r="19" spans="1:20" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="56"/>
-      <c r="B19" s="57"/>
-      <c r="C19" s="57"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="57"/>
-      <c r="H19" s="57"/>
-      <c r="I19" s="57"/>
-      <c r="J19" s="52" t="s">
+      <c r="A19" s="34"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="K19" s="52"/>
-      <c r="L19" s="52"/>
-      <c r="M19" s="52"/>
-      <c r="N19" s="52"/>
-      <c r="O19" s="54"/>
-      <c r="P19" s="55"/>
-      <c r="Q19" s="55"/>
-      <c r="R19" s="55"/>
-      <c r="S19" s="52"/>
-      <c r="T19" s="53"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="28"/>
+      <c r="M19" s="28"/>
+      <c r="N19" s="28"/>
+      <c r="O19" s="38"/>
+      <c r="P19" s="29"/>
+      <c r="Q19" s="29"/>
+      <c r="R19" s="29"/>
+      <c r="S19" s="28"/>
+      <c r="T19" s="33"/>
     </row>
     <row r="20" spans="1:20" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="58"/>
-      <c r="B20" s="59"/>
-      <c r="C20" s="59"/>
-      <c r="D20" s="59"/>
-      <c r="E20" s="59"/>
-      <c r="F20" s="59"/>
-      <c r="G20" s="59"/>
-      <c r="H20" s="59"/>
-      <c r="I20" s="59"/>
-      <c r="J20" s="60" t="s">
+      <c r="A20" s="36"/>
+      <c r="B20" s="37"/>
+      <c r="C20" s="37"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="37"/>
+      <c r="G20" s="37"/>
+      <c r="H20" s="37"/>
+      <c r="I20" s="37"/>
+      <c r="J20" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="K20" s="60"/>
-      <c r="L20" s="60"/>
-      <c r="M20" s="60"/>
-      <c r="N20" s="60"/>
-      <c r="O20" s="61">
+      <c r="K20" s="39"/>
+      <c r="L20" s="39"/>
+      <c r="M20" s="39"/>
+      <c r="N20" s="39"/>
+      <c r="O20" s="40">
         <f>SUM(O13:R19)*0.1</f>
         <v>0</v>
       </c>
-      <c r="P20" s="62"/>
-      <c r="Q20" s="62"/>
-      <c r="R20" s="62"/>
-      <c r="S20" s="60"/>
-      <c r="T20" s="63"/>
+      <c r="P20" s="41"/>
+      <c r="Q20" s="41"/>
+      <c r="R20" s="41"/>
+      <c r="S20" s="39"/>
+      <c r="T20" s="42"/>
     </row>
     <row r="21" spans="1:20" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="44" t="s">
+      <c r="A21" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="B21" s="45"/>
-      <c r="C21" s="45"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="45"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="45"/>
-      <c r="J21" s="45"/>
-      <c r="K21" s="45"/>
-      <c r="L21" s="45"/>
-      <c r="M21" s="45"/>
-      <c r="N21" s="45"/>
-      <c r="O21" s="46">
+      <c r="B21" s="44"/>
+      <c r="C21" s="44"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="44"/>
+      <c r="I21" s="44"/>
+      <c r="J21" s="44"/>
+      <c r="K21" s="44"/>
+      <c r="L21" s="44"/>
+      <c r="M21" s="44"/>
+      <c r="N21" s="44"/>
+      <c r="O21" s="45">
         <f>SUM(O13:R20)</f>
         <v>0</v>
       </c>
-      <c r="P21" s="46"/>
-      <c r="Q21" s="46"/>
-      <c r="R21" s="46"/>
-      <c r="S21" s="45"/>
-      <c r="T21" s="47"/>
+      <c r="P21" s="45"/>
+      <c r="Q21" s="45"/>
+      <c r="R21" s="45"/>
+      <c r="S21" s="44"/>
+      <c r="T21" s="46"/>
     </row>
     <row r="22" spans="1:20" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2"/>
@@ -5535,11 +5535,11 @@
       <c r="T22" s="2"/>
     </row>
     <row r="23" spans="1:20" s="5" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="50" t="s">
+      <c r="A23" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="B23" s="50"/>
-      <c r="C23" s="50"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="49"/>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
@@ -5559,134 +5559,171 @@
       <c r="T23" s="4"/>
     </row>
     <row r="24" spans="1:20" s="5" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="51" t="s">
+      <c r="A24" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="B24" s="50"/>
-      <c r="C24" s="50"/>
-      <c r="D24" s="50"/>
-      <c r="E24" s="50"/>
-      <c r="F24" s="50"/>
-      <c r="G24" s="50"/>
-      <c r="H24" s="50"/>
-      <c r="I24" s="50"/>
-      <c r="J24" s="50"/>
-      <c r="K24" s="50"/>
-      <c r="L24" s="50"/>
-      <c r="M24" s="50"/>
-      <c r="N24" s="50"/>
-      <c r="O24" s="50"/>
-      <c r="P24" s="50"/>
-      <c r="Q24" s="50"/>
-      <c r="R24" s="50"/>
-      <c r="S24" s="50"/>
-      <c r="T24" s="50"/>
+      <c r="B24" s="49"/>
+      <c r="C24" s="49"/>
+      <c r="D24" s="49"/>
+      <c r="E24" s="49"/>
+      <c r="F24" s="49"/>
+      <c r="G24" s="49"/>
+      <c r="H24" s="49"/>
+      <c r="I24" s="49"/>
+      <c r="J24" s="49"/>
+      <c r="K24" s="49"/>
+      <c r="L24" s="49"/>
+      <c r="M24" s="49"/>
+      <c r="N24" s="49"/>
+      <c r="O24" s="49"/>
+      <c r="P24" s="49"/>
+      <c r="Q24" s="49"/>
+      <c r="R24" s="49"/>
+      <c r="S24" s="49"/>
+      <c r="T24" s="49"/>
     </row>
     <row r="25" spans="1:20" s="5" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="51" t="s">
+      <c r="A25" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="50"/>
-      <c r="C25" s="50"/>
-      <c r="D25" s="50"/>
-      <c r="E25" s="50"/>
-      <c r="F25" s="50"/>
-      <c r="G25" s="50"/>
-      <c r="H25" s="50"/>
-      <c r="I25" s="50"/>
-      <c r="J25" s="50"/>
-      <c r="K25" s="50"/>
-      <c r="L25" s="50"/>
-      <c r="M25" s="50"/>
-      <c r="N25" s="50"/>
-      <c r="O25" s="50"/>
-      <c r="P25" s="50"/>
-      <c r="Q25" s="50"/>
-      <c r="R25" s="50"/>
-      <c r="S25" s="50"/>
-      <c r="T25" s="50"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="49"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="49"/>
+      <c r="G25" s="49"/>
+      <c r="H25" s="49"/>
+      <c r="I25" s="49"/>
+      <c r="J25" s="49"/>
+      <c r="K25" s="49"/>
+      <c r="L25" s="49"/>
+      <c r="M25" s="49"/>
+      <c r="N25" s="49"/>
+      <c r="O25" s="49"/>
+      <c r="P25" s="49"/>
+      <c r="Q25" s="49"/>
+      <c r="R25" s="49"/>
+      <c r="S25" s="49"/>
+      <c r="T25" s="49"/>
     </row>
     <row r="26" spans="1:20" s="5" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="51" t="s">
+      <c r="A26" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="50"/>
-      <c r="C26" s="50"/>
-      <c r="D26" s="50"/>
-      <c r="E26" s="50"/>
-      <c r="F26" s="50"/>
-      <c r="G26" s="50"/>
-      <c r="H26" s="50"/>
-      <c r="I26" s="50"/>
-      <c r="J26" s="50"/>
-      <c r="K26" s="50"/>
-      <c r="L26" s="50"/>
-      <c r="M26" s="50"/>
-      <c r="N26" s="50"/>
-      <c r="O26" s="50"/>
-      <c r="P26" s="50"/>
-      <c r="Q26" s="50"/>
-      <c r="R26" s="50"/>
-      <c r="S26" s="50"/>
-      <c r="T26" s="50"/>
+      <c r="B26" s="49"/>
+      <c r="C26" s="49"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="49"/>
+      <c r="G26" s="49"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="49"/>
+      <c r="J26" s="49"/>
+      <c r="K26" s="49"/>
+      <c r="L26" s="49"/>
+      <c r="M26" s="49"/>
+      <c r="N26" s="49"/>
+      <c r="O26" s="49"/>
+      <c r="P26" s="49"/>
+      <c r="Q26" s="49"/>
+      <c r="R26" s="49"/>
+      <c r="S26" s="49"/>
+      <c r="T26" s="49"/>
     </row>
     <row r="27" spans="1:20" s="5" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="51" t="s">
+      <c r="A27" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="50"/>
-      <c r="C27" s="50"/>
-      <c r="D27" s="50"/>
-      <c r="E27" s="50"/>
-      <c r="F27" s="50"/>
-      <c r="G27" s="50"/>
-      <c r="H27" s="50"/>
-      <c r="I27" s="50"/>
-      <c r="J27" s="50"/>
-      <c r="K27" s="50"/>
-      <c r="L27" s="50"/>
-      <c r="M27" s="50"/>
-      <c r="N27" s="50"/>
-      <c r="O27" s="50"/>
-      <c r="P27" s="50"/>
-      <c r="Q27" s="50"/>
-      <c r="R27" s="50"/>
-      <c r="S27" s="50"/>
-      <c r="T27" s="50"/>
+      <c r="B27" s="49"/>
+      <c r="C27" s="49"/>
+      <c r="D27" s="49"/>
+      <c r="E27" s="49"/>
+      <c r="F27" s="49"/>
+      <c r="G27" s="49"/>
+      <c r="H27" s="49"/>
+      <c r="I27" s="49"/>
+      <c r="J27" s="49"/>
+      <c r="K27" s="49"/>
+      <c r="L27" s="49"/>
+      <c r="M27" s="49"/>
+      <c r="N27" s="49"/>
+      <c r="O27" s="49"/>
+      <c r="P27" s="49"/>
+      <c r="Q27" s="49"/>
+      <c r="R27" s="49"/>
+      <c r="S27" s="49"/>
+      <c r="T27" s="49"/>
     </row>
     <row r="28" spans="1:20" ht="96.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="48" t="s">
+      <c r="A28" s="47" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="49"/>
-      <c r="C28" s="49"/>
-      <c r="D28" s="49"/>
-      <c r="E28" s="49"/>
-      <c r="F28" s="49"/>
-      <c r="G28" s="49"/>
-      <c r="H28" s="49"/>
-      <c r="I28" s="49"/>
-      <c r="J28" s="49"/>
-      <c r="K28" s="49"/>
-      <c r="L28" s="49"/>
-      <c r="M28" s="49"/>
-      <c r="N28" s="49"/>
-      <c r="O28" s="49"/>
-      <c r="P28" s="49"/>
-      <c r="Q28" s="49"/>
-      <c r="R28" s="49"/>
-      <c r="S28" s="49"/>
-      <c r="T28" s="49"/>
+      <c r="B28" s="48"/>
+      <c r="C28" s="48"/>
+      <c r="D28" s="48"/>
+      <c r="E28" s="48"/>
+      <c r="F28" s="48"/>
+      <c r="G28" s="48"/>
+      <c r="H28" s="48"/>
+      <c r="I28" s="48"/>
+      <c r="J28" s="48"/>
+      <c r="K28" s="48"/>
+      <c r="L28" s="48"/>
+      <c r="M28" s="48"/>
+      <c r="N28" s="48"/>
+      <c r="O28" s="48"/>
+      <c r="P28" s="48"/>
+      <c r="Q28" s="48"/>
+      <c r="R28" s="48"/>
+      <c r="S28" s="48"/>
+      <c r="T28" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="67">
-    <mergeCell ref="F12:I12"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="A13:N13"/>
-    <mergeCell ref="O13:R13"/>
-    <mergeCell ref="J12:L12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="O12:R12"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="F11:I11"/>
+    <mergeCell ref="J11:L11"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="O11:R11"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A4:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D4:H5"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="N4:T4"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="N6:T6"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="F9:J9"/>
+    <mergeCell ref="M9:P9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="A21:N21"/>
+    <mergeCell ref="O21:R21"/>
+    <mergeCell ref="S21:T21"/>
+    <mergeCell ref="A28:T28"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A24:T24"/>
+    <mergeCell ref="A25:T25"/>
+    <mergeCell ref="A26:T26"/>
+    <mergeCell ref="A27:T27"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="J16:N16"/>
+    <mergeCell ref="O16:R16"/>
+    <mergeCell ref="S16:T16"/>
+    <mergeCell ref="J17:N17"/>
+    <mergeCell ref="O17:R17"/>
+    <mergeCell ref="S17:T17"/>
     <mergeCell ref="S13:T13"/>
     <mergeCell ref="A14:I20"/>
     <mergeCell ref="J14:N14"/>
@@ -5703,50 +5740,13 @@
     <mergeCell ref="S18:T18"/>
     <mergeCell ref="J19:N19"/>
     <mergeCell ref="O19:R19"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="J16:N16"/>
-    <mergeCell ref="O16:R16"/>
-    <mergeCell ref="S16:T16"/>
-    <mergeCell ref="J17:N17"/>
-    <mergeCell ref="O17:R17"/>
-    <mergeCell ref="S17:T17"/>
-    <mergeCell ref="A21:N21"/>
-    <mergeCell ref="O21:R21"/>
-    <mergeCell ref="S21:T21"/>
-    <mergeCell ref="A28:T28"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A24:T24"/>
-    <mergeCell ref="A25:T25"/>
-    <mergeCell ref="A26:T26"/>
-    <mergeCell ref="A27:T27"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="R5:S5"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="F9:J9"/>
-    <mergeCell ref="M9:P9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="A2:O2"/>
-    <mergeCell ref="A4:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D4:H5"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:G7"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="N4:T4"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="N6:T6"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="F11:I11"/>
-    <mergeCell ref="J11:L11"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="O11:R11"/>
+    <mergeCell ref="F12:I12"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="A13:N13"/>
+    <mergeCell ref="O13:R13"/>
+    <mergeCell ref="J12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="O12:R12"/>
   </mergeCells>
   <phoneticPr fontId="28" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
